--- a/Supplementary_table_3.xlsx
+++ b/Supplementary_table_3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Orchidaceae\Papers\Greek_Armenia_Orchid_work\data_for_analysis\Cleaned_datasets\for_publication\Figures\Supplementary\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anner\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C13AE11B-3E28-450E-8F65-187C6FA93F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02FD802F-23E0-4645-935E-3E9A7ED3188D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{E9610134-F910-437B-A0F9-1B1652404BB1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{E9610134-F910-437B-A0F9-1B1652404BB1}"/>
   </bookViews>
   <sheets>
     <sheet name="Testing_Combined_Stats" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="60">
   <si>
     <t>Te</t>
   </si>
@@ -53,15 +53,9 @@
     <t>T</t>
   </si>
   <si>
-    <t>Dilijan*Parz lake district, before the "Caucasian Red Deer Breeding Center"; Dilijan, Tavush</t>
-  </si>
-  <si>
     <t>Platanthera chlorantha</t>
   </si>
   <si>
-    <t>Between v.v. Hermon*Karmrashen; Yeghegis, Vayots Dzor</t>
-  </si>
-  <si>
     <t>Orchis mascula</t>
   </si>
   <si>
@@ -83,9 +77,6 @@
     <t>Dactylorhiza salina</t>
   </si>
   <si>
-    <t>Yeghegis valley, along the river; Yeghegis, Vayots Dzor</t>
-  </si>
-  <si>
     <t>Dactylorhiza merovensis</t>
   </si>
   <si>
@@ -95,9 +86,6 @@
     <t>E</t>
   </si>
   <si>
-    <t>Getahovit*Yenokavan road, right of the road, forest clearing; Ijevan, Tavush</t>
-  </si>
-  <si>
     <t>Cephalanthera damasonium</t>
   </si>
   <si>
@@ -219,6 +207,21 @@
   </si>
   <si>
     <t>Max_FG_perc</t>
+  </si>
+  <si>
+    <t>Getahovit -Enoqavan road, right of the road, forest clearing; Ijevan, Tavush</t>
+  </si>
+  <si>
+    <t>Getahovit-Enoqavan road, right of the road, forest clearing; Ijevan, Tavush</t>
+  </si>
+  <si>
+    <t>Eghegis valley, along the river; Eghegis, Vayots Dzor</t>
+  </si>
+  <si>
+    <t>Between v.v. Hermon&amp;Karmrashen; Eghegis, Vayots Dzor</t>
+  </si>
+  <si>
+    <t>Dilijan-Parz lake district, before the "Caucasian Red Deer Breeding Center"; Dilijan, Tavush</t>
   </si>
 </sst>
 </file>
@@ -581,64 +584,64 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E45F9B1-A226-4FB5-BAA1-A8BDEAF6B335}">
   <dimension ref="A1:M27"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="83.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="45.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="83.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="J1" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C2">
         <v>20</v>
@@ -674,12 +677,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C3">
         <v>20</v>
@@ -715,12 +718,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C4">
         <v>20</v>
@@ -756,12 +759,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C5">
         <v>20</v>
@@ -797,12 +800,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C6">
         <v>20</v>
@@ -826,24 +829,24 @@
         <v>0</v>
       </c>
       <c r="J6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K6" t="s">
         <v>2</v>
       </c>
       <c r="L6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="M6" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C7">
         <v>20</v>
@@ -867,24 +870,24 @@
         <v>0</v>
       </c>
       <c r="J7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K7" t="s">
         <v>2</v>
       </c>
       <c r="L7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="M7" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C8">
         <v>20</v>
@@ -908,24 +911,24 @@
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K8" t="s">
         <v>2</v>
       </c>
       <c r="L8" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="M8" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C9">
         <v>20</v>
@@ -961,12 +964,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C10">
         <v>20</v>
@@ -1002,12 +1005,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C11">
         <v>20</v>
@@ -1043,12 +1046,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C12">
         <v>20</v>
@@ -1072,24 +1075,24 @@
         <v>0</v>
       </c>
       <c r="J12" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K12" t="s">
         <v>2</v>
       </c>
       <c r="L12" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="M12" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C13">
         <v>20</v>
@@ -1125,12 +1128,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C14">
         <v>20</v>
@@ -1166,12 +1169,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C15">
         <v>20</v>
@@ -1207,12 +1210,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C16">
         <v>20</v>
@@ -1248,12 +1251,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C17">
         <v>20</v>
@@ -1289,12 +1292,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C18">
         <v>20</v>
@@ -1330,12 +1333,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C19">
         <v>20</v>
@@ -1371,12 +1374,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="C20">
         <v>20</v>
@@ -1412,12 +1415,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -1441,24 +1444,24 @@
         <v>0</v>
       </c>
       <c r="J21" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K21" t="s">
         <v>2</v>
       </c>
       <c r="L21" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="M21" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="C22">
         <v>20</v>
@@ -1494,12 +1497,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C23">
         <v>20</v>
@@ -1535,12 +1538,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C24">
         <v>20</v>
@@ -1576,12 +1579,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B25" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C25">
         <v>20</v>
@@ -1617,12 +1620,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B26" t="s">
-        <v>5</v>
+        <v>58</v>
       </c>
       <c r="C26">
         <v>20</v>
@@ -1658,12 +1661,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B27" t="s">
-        <v>3</v>
+        <v>59</v>
       </c>
       <c r="C27">
         <v>20</v>
